--- a/metrics/Global_Metrics_Augmented_Lags_WL_DI.xlsx
+++ b/metrics/Global_Metrics_Augmented_Lags_WL_DI.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.17009424235066</v>
+        <v>2.117937148746338</v>
       </c>
       <c r="C2" t="n">
-        <v>2.183328431427897</v>
+        <v>2.072845440643849</v>
       </c>
       <c r="D2" t="n">
-        <v>6.189487718603804</v>
+        <v>5.99115689853489</v>
       </c>
       <c r="E2" t="n">
-        <v>2.487868107155965</v>
+        <v>2.447683986656548</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9223712028840617</v>
+        <v>0.9327090308371154</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9604083718006752</v>
+        <v>0.9660379103621054</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9627379089956352</v>
+        <v>0.9677968964413429</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8399054149885405</v>
+        <v>0.853733380718812</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006346115437099176</v>
+        <v>2.669934765570445</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09801258365986421</v>
+        <v>2.504681887942086</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4817107184163293</v>
+        <v>8.267983427535862</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4826915725859071</v>
+        <v>2.875410132056967</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4159774625636544</v>
+        <v>0.9111739144763189</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08560591869244827</v>
+        <v>0.9661736193053387</v>
       </c>
       <c r="P2" t="n">
-        <v>0.151529308836747</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9738277057349897</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8850322386773514</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.294796012365692</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.316562505575269</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.627925820957452</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.574475834215084</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.910525797485903</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9560782094031465</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9533542637494467</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8257497801241356</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.81197241055746</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.604594567565202</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.784316157291358</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.187307970380796</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9430522827493868</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9744089615804281</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9775624705258499</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8825938827556751</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01093935262369311</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1701920646827415</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.005992870039059017</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.007014907026674122</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.01600441291872778</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1629108867089157</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2097556097749527</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2249235900791727</v>
+        <v>0.2297276250713507</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1535431725213592</v>
+        <v>0.1636379456519212</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1145467493692646</v>
+        <v>0.103940339577394</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3384475577829815</v>
+        <v>0.322397797103817</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9795715100655769</v>
+        <v>0.9834167461310663</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9898123564127255</v>
+        <v>0.9916980119644198</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9941508911257227</v>
+        <v>0.9939392080890589</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9367474460157068</v>
+        <v>0.9360415138170665</v>
       </c>
       <c r="J3" t="n">
-        <v>0.004282817120462301</v>
+        <v>0.2030439827278697</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03692436890812731</v>
+        <v>0.1262328841493522</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4960161899366491</v>
+        <v>0.08311122226058312</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4961260243406073</v>
+        <v>0.2882901702462002</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4643948561088609</v>
+        <v>0.9850912511715346</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01936747113890548</v>
+        <v>0.9935412152136236</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01630401735536223</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9940078164210213</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9459220720631618</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1307647700316365</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.101516729889647</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.03102507782134541</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1761393704466591</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9895070790695368</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9969857476713356</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9965249885968432</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9575282908017203</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2983177558645126</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.2227496269932416</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1549021578284285</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.3935761144028287</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9777364680470603</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9895290878504844</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9901663058417293</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9258766676027861</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.004384261210511553</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.04280390669023296</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.00219956755317946</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.001966277437166986</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.009208886324651278</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.03203718262567259</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.02977382664221002</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6459233496795328</v>
+        <v>0.7051088071083338</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3852264496075319</v>
+        <v>0.4436950432296922</v>
       </c>
       <c r="D4" t="n">
-        <v>1.000157144230503</v>
+        <v>1.044237771392862</v>
       </c>
       <c r="E4" t="n">
-        <v>1.000078569028705</v>
+        <v>1.021879528806044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9842066703070664</v>
+        <v>0.9852292163653398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9920843816494448</v>
+        <v>0.992590921688011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9900307418157483</v>
+        <v>0.9862316155427162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9238659470557222</v>
+        <v>0.9136895286459391</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002951620421371537</v>
+        <v>0.7200167079167226</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09376425301584768</v>
+        <v>0.5452094066193983</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4966382462248635</v>
+        <v>0.8564101339183927</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4929325818488368</v>
+        <v>0.9254242993991419</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4550912309597037</v>
+        <v>0.9898292068029269</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05658583210057089</v>
+        <v>0.9950575313900767</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03762437091637486</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9876721872776174</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9291046014397268</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.8294052247750603</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5024046383727189</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.584751296031465</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.258869054362472</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9611607227734766</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9881982086500842</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9760026771403567</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8919395131912481</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.6257262475416111</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.3607887594034316</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7909108480449053</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.8893316861806427</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9898718852303459</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9956452927277175</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9905561155886843</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9286584250473939</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.004123377170183462</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1381966472178761</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.002091127759280276</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.004551551356443584</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01314807027606935</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.0941973001001572</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.06850438930491709</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
